--- a/docs/BUG_TRACKER.xlsx
+++ b/docs/BUG_TRACKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\source\repos\DailyVitalsApp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2788C3E7-4D91-420F-A4F2-906274E9DAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60F2AAE-2A82-4C33-BB75-E1DCC9E053FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="185">
   <si>
     <t>Bug ID</t>
   </si>
@@ -578,6 +578,21 @@
   </si>
   <si>
     <t>The details modal pop message should show values</t>
+  </si>
+  <si>
+    <t>feature/blood-pressure-save</t>
+  </si>
+  <si>
+    <t>SSR form-post binding failure</t>
+  </si>
+  <si>
+    <t>page isn't working message</t>
+  </si>
+  <si>
+    <t>page comes back with page isn't working</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-011.png</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1259,9 @@
       <c r="I5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="K5" s="2" t="s">
         <v>32</v>
       </c>
@@ -1254,7 +1271,9 @@
       <c r="M5" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s">
+        <v>181</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2" t="s">
         <v>30</v>
@@ -1553,19 +1572,33 @@
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="B12" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1573,9 +1606,9 @@
         <v>30</v>
       </c>
       <c r="Q12" s="3"/>
-      <c r="R12" s="4" t="str">
+      <c r="R12" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2212,7 +2245,7 @@
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="4" t="str">
-        <f t="shared" ref="R34:R65" ca="1" si="1">IF(B34="","",IF(Q34&lt;&gt;"",Q34-B34,TODAY()-B34))</f>
+        <f t="shared" ref="R34:R51" ca="1" si="1">IF(B34="","",IF(Q34&lt;&gt;"",Q34-B34,TODAY()-B34))</f>
         <v/>
       </c>
     </row>
@@ -2829,7 +2862,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Bug Tracker'!F2:F51,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
@@ -2845,7 +2878,7 @@
       </c>
       <c r="H5" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G5)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2854,7 +2887,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIFS('Bug Tracker'!F2:F51,"&lt;&gt;",'Bug Tracker'!K2:K51,"&lt;&gt;Closed",'Bug Tracker'!K2:K51,"&lt;&gt;Verified")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
@@ -2879,7 +2912,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"Critical")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">

--- a/docs/BUG_TRACKER.xlsx
+++ b/docs/BUG_TRACKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\source\repos\DailyVitalsApp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60F2AAE-2A82-4C33-BB75-E1DCC9E053FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F14DCB-38B7-4CF1-AC7B-9BEA569C8F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="215">
   <si>
     <t>Bug ID</t>
   </si>
@@ -593,6 +593,128 @@
   </si>
   <si>
     <t>docs/screenshots/AV-011.png</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">production sign-in page was using Blazor SSR/interactive </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EditForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> submission for authentication</t>
+    </r>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>returning to blood pressure entry screen came back with development mode</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-012.png</t>
+  </si>
+  <si>
+    <t>feature/page-load-bp-error</t>
+  </si>
+  <si>
+    <t>form view shows and saves</t>
+  </si>
+  <si>
+    <t>selected value should be able to delete but button remains disabled</t>
+  </si>
+  <si>
+    <t>bp delete button remains disabled</t>
+  </si>
+  <si>
+    <t>selected bp reading should be able to delete</t>
+  </si>
+  <si>
+    <t>remains disabled</t>
+  </si>
+  <si>
+    <t>feature/glucose-save-error</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Converted Weight from Blazor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EditForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> postback to a normal server POST</t>
+    </r>
+  </si>
+  <si>
+    <t>9e18ea9</t>
+  </si>
+  <si>
+    <t>1d14b8a</t>
+  </si>
+  <si>
+    <t>BMI now recalculates when the user types a weight or changes uni</t>
+  </si>
+  <si>
+    <t>592e5fd</t>
+  </si>
+  <si>
+    <t>uses a tiny JS helper, so it doesn’t depend on Blazor state refresh timing</t>
+  </si>
+  <si>
+    <t>nutrition sub menu error</t>
+  </si>
+  <si>
+    <t>Nutrition</t>
+  </si>
+  <si>
+    <t>nutrition sub menu fails loading all sub menus</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-014.png</t>
+  </si>
+  <si>
+    <t>same error as other save actions - form goes blank pops required validations</t>
+  </si>
+  <si>
+    <t>fluid intake save error</t>
+  </si>
+  <si>
+    <t>Hydration</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-015.png</t>
+  </si>
+  <si>
+    <t>kidney lab entry save error</t>
+  </si>
+  <si>
+    <t>Kidney Labs</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-016.png</t>
+  </si>
+  <si>
+    <t>all helper modal buttons on kidney lab panel aren't popping</t>
+  </si>
+  <si>
+    <t>kidney lab pop</t>
   </si>
 </sst>
 </file>
@@ -602,7 +724,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -636,6 +758,10 @@
       <sz val="11"/>
       <color rgb="FF17324D"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="4">
@@ -820,6 +946,14 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BugTrackerTable" displayName="BugTrackerTable" ref="A1:R51">
+  <autoFilter ref="A1:R51" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Investigating"/>
+        <filter val="Open"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Bug ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date Reported"/>
@@ -1023,7 +1157,7 @@
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="34" customWidth="1"/>
-    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="14" max="14" width="80.83203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
@@ -1231,7 +1365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="28">
+    <row r="5" spans="1:18" ht="28" hidden="1">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1263,7 +1397,7 @@
         <v>180</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>145</v>
@@ -1284,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="28">
+    <row r="6" spans="1:18" ht="28" hidden="1">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1312,9 +1446,11 @@
       <c r="I6" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="K6" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>156</v>
@@ -1333,7 +1469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="28">
+    <row r="7" spans="1:18" ht="28" hidden="1">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -1363,24 +1499,30 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>161</v>
       </c>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+      <c r="N7" t="s">
+        <v>199</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="P7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>46216</v>
+      </c>
       <c r="R7" s="4">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="28">
+    <row r="8" spans="1:18" ht="28" hidden="1">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
@@ -1410,16 +1552,20 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>162</v>
       </c>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="N8" t="s">
+        <v>196</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="P8" s="2" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="4">
@@ -1427,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="42">
+    <row r="9" spans="1:18" ht="42" hidden="1">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -1457,18 +1603,24 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>163</v>
       </c>
       <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="N9" t="s">
+        <v>201</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="P9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>46216</v>
+      </c>
       <c r="R9" s="4">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
@@ -1568,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" hidden="1">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -1591,67 +1743,111 @@
         <v>183</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>184</v>
       </c>
       <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="N12" t="s">
+        <v>185</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q12" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>46216</v>
+      </c>
       <c r="R12" s="4">
         <f t="shared" ca="1" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" ht="28" hidden="1">
       <c r="A13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="B13" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="K13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>46216</v>
+      </c>
+      <c r="R13" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="28">
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="B14" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
         <v>32</v>
@@ -1664,28 +1860,44 @@
         <v>30</v>
       </c>
       <c r="Q14" s="3"/>
-      <c r="R14" s="4" t="str">
+      <c r="R14" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="B15" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>204</v>
+      </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -1693,28 +1905,42 @@
         <v>30</v>
       </c>
       <c r="Q15" s="3"/>
-      <c r="R15" s="4" t="str">
+      <c r="R15" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="28">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
+      <c r="B16" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -1722,28 +1948,42 @@
         <v>30</v>
       </c>
       <c r="Q16" s="3"/>
-      <c r="R16" s="4" t="str">
+      <c r="R16" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="28">
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
+      <c r="B17" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -1751,23 +1991,37 @@
         <v>30</v>
       </c>
       <c r="Q17" s="3"/>
-      <c r="R17" s="4" t="str">
+      <c r="R17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="28">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
+      <c r="B18" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>213</v>
+      </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
         <v>32</v>
@@ -1780,9 +2034,9 @@
         <v>30</v>
       </c>
       <c r="Q18" s="3"/>
-      <c r="R18" s="4" t="str">
+      <c r="R18" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -2862,7 +3116,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Bug Tracker'!F2:F51,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
@@ -2870,7 +3124,7 @@
       </c>
       <c r="E5" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D5)</f>
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -2878,7 +3132,7 @@
       </c>
       <c r="H5" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G5)</f>
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2887,7 +3141,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIFS('Bug Tracker'!F2:F51,"&lt;&gt;",'Bug Tracker'!K2:K51,"&lt;&gt;Closed",'Bug Tracker'!K2:K51,"&lt;&gt;Verified")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
@@ -2903,7 +3157,7 @@
       </c>
       <c r="H6" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2912,7 +3166,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"Critical")</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
@@ -2937,7 +3191,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"High")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
@@ -3002,7 +3256,7 @@
       </c>
       <c r="B11" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,"Closed")+COUNTIF('Bug Tracker'!K2:K51,"Verified")</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
@@ -3040,7 +3294,7 @@
       </c>
       <c r="E13" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D13)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>

--- a/docs/BUG_TRACKER.xlsx
+++ b/docs/BUG_TRACKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\source\repos\DailyVitalsApp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F14DCB-38B7-4CF1-AC7B-9BEA569C8F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD50265C-C818-4EF4-8C9D-E4E03FBBFBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="252">
   <si>
     <t>Bug ID</t>
   </si>
@@ -715,6 +715,149 @@
   </si>
   <si>
     <t>kidney lab pop</t>
+  </si>
+  <si>
+    <t>time of entry is not default setting to CST, is this a setting in profile and then it will be according to the user local</t>
+  </si>
+  <si>
+    <t>Data Issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CST time value </t>
+  </si>
+  <si>
+    <t>should be CST</t>
+  </si>
+  <si>
+    <t>appears east coat</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-017.png</t>
+  </si>
+  <si>
+    <t>hide Renal Friendly Foods menu for now</t>
+  </si>
+  <si>
+    <t>Enhancement</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>needs to be restructured to global foods not person specific</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-018.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-019.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-020.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-021.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-022.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-023.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-024.png</t>
+  </si>
+  <si>
+    <t>plain server POST endpoint</t>
+  </si>
+  <si>
+    <t>feature/add-new-exercise</t>
+  </si>
+  <si>
+    <t>35d218d</t>
+  </si>
+  <si>
+    <t>delete button remains disabled for selected item, it should be able to delete as normal</t>
+  </si>
+  <si>
+    <t>delete button disabled</t>
+  </si>
+  <si>
+    <t>make selection and delete work through normal browser/server requests</t>
+  </si>
+  <si>
+    <t>932b0c2</t>
+  </si>
+  <si>
+    <t>feature/exercise-delete-button-disabled</t>
+  </si>
+  <si>
+    <t>move the save action out of Blazor validation and into a server endpoint</t>
+  </si>
+  <si>
+    <t>66b11c5</t>
+  </si>
+  <si>
+    <t>fluid intake delete</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">verify the menu no longer has those fragile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@onclick</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> submenu buttons</t>
+    </r>
+  </si>
+  <si>
+    <t>feature/nutrition-sub-menu-load-failure</t>
+  </si>
+  <si>
+    <t>fa23273</t>
+  </si>
+  <si>
+    <t>add food item on save blanks fields out does nothing</t>
+  </si>
+  <si>
+    <t>nutrition save error</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">the modal exists, but the Details buttons are </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@onclick</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> only</t>
+    </r>
+  </si>
+  <si>
+    <t>d4b5ee6</t>
+  </si>
+  <si>
+    <t>8cfb9c4</t>
+  </si>
+  <si>
+    <t>remove delete button</t>
   </si>
 </sst>
 </file>
@@ -949,7 +1092,6 @@
   <autoFilter ref="A1:R51" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="10">
       <filters>
-        <filter val="Investigating"/>
         <filter val="Open"/>
       </filters>
     </filterColumn>
@@ -1153,7 +1295,7 @@
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="38" customWidth="1"/>
     <col min="8" max="9" width="32" customWidth="1"/>
-    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="34" customWidth="1"/>
@@ -1220,7 +1362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="42">
+    <row r="2" spans="1:18" ht="42" hidden="1">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -1252,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>28</v>
@@ -1268,7 +1410,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="4">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(B2="","",IF(Q2&lt;&gt;"",Q2-B2,TODAY()-B2))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="28">
@@ -1315,7 +1457,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="28">
@@ -1362,7 +1504,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="28" hidden="1">
@@ -1415,7 +1557,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="28" hidden="1">
@@ -1466,7 +1608,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="28" hidden="1">
@@ -1570,7 +1712,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="42" hidden="1">
@@ -1626,7 +1768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="28">
+    <row r="10" spans="1:18" ht="28" hidden="1">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
@@ -1654,26 +1796,32 @@
       <c r="I10" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="J10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="K10" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>164</v>
       </c>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+      <c r="N10" t="s">
+        <v>232</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="P10" s="2" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="28" hidden="1">
       <c r="A11" s="2" t="s">
         <v>40</v>
       </c>
@@ -1703,21 +1851,27 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>165</v>
       </c>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="N11" t="s">
+        <v>248</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="P11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q11" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>46217</v>
+      </c>
       <c r="R11" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18" hidden="1">
@@ -1820,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="28">
+    <row r="14" spans="1:18" ht="28" hidden="1">
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
@@ -1850,22 +2004,28 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>250</v>
+      </c>
       <c r="P14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>46217</v>
+      </c>
       <c r="R14" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" hidden="1">
       <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
@@ -1891,26 +2051,34 @@
       <c r="I15" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="K15" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>205</v>
       </c>
       <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="N15" t="s">
+        <v>243</v>
+      </c>
+      <c r="O15" t="s">
+        <v>245</v>
+      </c>
       <c r="P15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q15" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>46217</v>
+      </c>
       <c r="R15" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="28" hidden="1">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -1936,21 +2104,27 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>209</v>
       </c>
       <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="N16" t="s">
+        <v>240</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="P16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q16" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>46217</v>
+      </c>
       <c r="R16" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="28">
@@ -1993,7 +2167,7 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="28">
@@ -2026,7 +2200,9 @@
       <c r="K18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" s="2" t="s">
+        <v>220</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2036,26 +2212,44 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="42">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
+      <c r="B19" s="3">
+        <v>46217</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L19" s="2"/>
+      <c r="L19" s="2" t="s">
+        <v>225</v>
+      </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2063,28 +2257,42 @@
         <v>30</v>
       </c>
       <c r="Q19" s="3"/>
-      <c r="R19" s="4" t="str">
+      <c r="R19" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="28">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="B20" s="3">
+        <v>46217</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>224</v>
+      </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2092,57 +2300,93 @@
         <v>30</v>
       </c>
       <c r="Q20" s="3"/>
-      <c r="R20" s="4" t="str">
+      <c r="R20" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="28" hidden="1">
       <c r="A21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
+      <c r="B21" s="3">
+        <v>46217</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="J21" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="K21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="N21" t="s">
+        <v>237</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="P21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>46217</v>
+      </c>
+      <c r="R21" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="28">
       <c r="A22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="B22" s="3">
+        <v>46217</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L22" s="2"/>
+      <c r="L22" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2150,28 +2394,42 @@
         <v>30</v>
       </c>
       <c r="Q22" s="3"/>
-      <c r="R22" s="4" t="str">
+      <c r="R22" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="28">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
+      <c r="B23" s="3">
+        <v>46217</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L23" s="2"/>
+      <c r="L23" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -2179,20 +2437,30 @@
         <v>30</v>
       </c>
       <c r="Q23" s="3"/>
-      <c r="R23" s="4" t="str">
+      <c r="R23" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="B24" s="3">
+        <v>46217</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2200,7 +2468,9 @@
       <c r="K24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" s="2" t="s">
+        <v>231</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -2208,9 +2478,9 @@
         <v>30</v>
       </c>
       <c r="Q24" s="3"/>
-      <c r="R24" s="4" t="str">
+      <c r="R24" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -3047,8 +3317,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3116,7 +3387,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Bug Tracker'!F2:F51,"&lt;&gt;")</f>
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
@@ -3124,7 +3395,7 @@
       </c>
       <c r="E5" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D5)</f>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -3132,7 +3403,7 @@
       </c>
       <c r="H5" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G5)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3141,7 +3412,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIFS('Bug Tracker'!F2:F51,"&lt;&gt;",'Bug Tracker'!K2:K51,"&lt;&gt;Closed",'Bug Tracker'!K2:K51,"&lt;&gt;Verified")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
@@ -3149,7 +3420,7 @@
       </c>
       <c r="E6" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
@@ -3157,7 +3428,7 @@
       </c>
       <c r="H6" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G6)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3166,7 +3437,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"Critical")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
@@ -3191,7 +3462,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"High")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
@@ -3207,7 +3478,7 @@
       </c>
       <c r="H8" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G8)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3256,7 +3527,7 @@
       </c>
       <c r="B11" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,"Closed")+COUNTIF('Bug Tracker'!K2:K51,"Verified")</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
@@ -3294,7 +3565,7 @@
       </c>
       <c r="E13" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D13)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>

--- a/docs/BUG_TRACKER.xlsx
+++ b/docs/BUG_TRACKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\source\repos\DailyVitalsApp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD50265C-C818-4EF4-8C9D-E4E03FBBFBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D07055B-BE61-40C9-A9A7-9B89ECB2AA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="272">
   <si>
     <t>Bug ID</t>
   </si>
@@ -858,6 +858,66 @@
   </si>
   <si>
     <t>remove delete button</t>
+  </si>
+  <si>
+    <t>time change should automatically update the Notes as shown, does nothing</t>
+  </si>
+  <si>
+    <t>update time</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-025.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-026.png</t>
+  </si>
+  <si>
+    <t>delete button is remains disabled, user should be able to change fluid records</t>
+  </si>
+  <si>
+    <t>disable delete button</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-027.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-028.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-030.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-031.png</t>
+  </si>
+  <si>
+    <t>all buttons New, Delete and Save are inoperable</t>
+  </si>
+  <si>
+    <t>inoperable buttons</t>
+  </si>
+  <si>
+    <t>23f1cbe</t>
+  </si>
+  <si>
+    <t>New button should reset the page and clear the validation errors but does nothing</t>
+  </si>
+  <si>
+    <t>New button inoperable</t>
+  </si>
+  <si>
+    <t>Save blanks out form and does not save newly entered food item</t>
+  </si>
+  <si>
+    <t>Save new food inoperable</t>
+  </si>
+  <si>
+    <t>interactive server connection is falling back to a normal POST</t>
+  </si>
+  <si>
+    <t>feature/inoperable-save-new-food-button</t>
+  </si>
+  <si>
+    <t>56abd35  58ecfef  3ba3a1c</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1470,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="4">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(B2="","",IF(Q2&lt;&gt;"",Q2-B2,TODAY()-B2))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="28">
@@ -1443,7 +1503,7 @@
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>137</v>
@@ -1457,10 +1517,10 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="28" hidden="1">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -1490,7 +1550,7 @@
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>141</v>
@@ -1504,7 +1564,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="28" hidden="1">
@@ -1557,7 +1617,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="28" hidden="1">
@@ -1608,7 +1668,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="28" hidden="1">
@@ -1712,7 +1772,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="42" hidden="1">
@@ -1818,7 +1878,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="28" hidden="1">
@@ -2127,7 +2187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="28">
+    <row r="17" spans="1:18" ht="28" hidden="1">
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
@@ -2153,7 +2213,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>212</v>
@@ -2162,15 +2222,15 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="28" hidden="1">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -2198,7 +2258,7 @@
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>220</v>
@@ -2212,10 +2272,10 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="42" hidden="1">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
@@ -2245,7 +2305,7 @@
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>225</v>
@@ -2259,10 +2319,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="28" hidden="1">
       <c r="A20" s="2" t="s">
         <v>49</v>
       </c>
@@ -2288,7 +2348,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>226</v>
@@ -2302,7 +2362,7 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="28" hidden="1">
@@ -2356,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="28">
+    <row r="22" spans="1:18" ht="28" hidden="1">
       <c r="A22" s="2" t="s">
         <v>51</v>
       </c>
@@ -2382,7 +2442,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>228</v>
@@ -2391,15 +2451,17 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q22" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>46218</v>
+      </c>
       <c r="R22" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="28" hidden="1">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -2425,7 +2487,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>229</v>
@@ -2434,15 +2496,17 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>46218</v>
+      </c>
       <c r="R23" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" hidden="1">
       <c r="A24" s="2" t="s">
         <v>53</v>
       </c>
@@ -2466,7 +2530,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>231</v>
@@ -2480,26 +2544,40 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="28" hidden="1">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="B25" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -2507,183 +2585,283 @@
         <v>30</v>
       </c>
       <c r="Q25" s="3"/>
-      <c r="R25" s="4" t="str">
+      <c r="R25" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" hidden="1">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="B26" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="Q26" s="3"/>
-      <c r="R26" s="4" t="str">
+      <c r="R26" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="28" hidden="1">
       <c r="A27" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="B27" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>46218</v>
+      </c>
+      <c r="R27" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="28" hidden="1">
       <c r="A28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
+      <c r="B28" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>258</v>
+      </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>46218</v>
+      </c>
+      <c r="R28" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="28" hidden="1">
       <c r="A29" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="B29" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>262</v>
+      </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>259</v>
+      </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+      <c r="O29" s="2" t="s">
+        <v>264</v>
+      </c>
       <c r="P29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>46218</v>
+      </c>
+      <c r="R29" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="28" hidden="1">
       <c r="A30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
+      <c r="B30" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L30" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>46218</v>
+      </c>
+      <c r="R30" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="28" hidden="1">
       <c r="A31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="B31" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>267</v>
+      </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>270</v>
+      </c>
       <c r="K31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+      <c r="N31" t="s">
+        <v>269</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>271</v>
+      </c>
       <c r="P31" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>46218</v>
+      </c>
+      <c r="R31" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -3387,7 +3565,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Bug Tracker'!F2:F51,"&lt;&gt;")</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
@@ -3395,7 +3573,7 @@
       </c>
       <c r="E5" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D5)</f>
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -3403,7 +3581,7 @@
       </c>
       <c r="H5" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G5)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3412,7 +3590,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIFS('Bug Tracker'!F2:F51,"&lt;&gt;",'Bug Tracker'!K2:K51,"&lt;&gt;Closed",'Bug Tracker'!K2:K51,"&lt;&gt;Verified")</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
@@ -3428,7 +3606,7 @@
       </c>
       <c r="H6" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G6)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3437,7 +3615,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"Critical")</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
@@ -3462,7 +3640,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"High")</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
@@ -3478,7 +3656,7 @@
       </c>
       <c r="H8" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G8)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3527,7 +3705,7 @@
       </c>
       <c r="B11" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,"Closed")+COUNTIF('Bug Tracker'!K2:K51,"Verified")</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
@@ -3565,7 +3743,7 @@
       </c>
       <c r="E13" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D13)</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>

--- a/docs/BUG_TRACKER.xlsx
+++ b/docs/BUG_TRACKER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\source\repos\DailyVitalsApp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D07055B-BE61-40C9-A9A7-9B89ECB2AA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203985B3-FB50-49DB-9C2B-9EB8D122B4E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="319">
   <si>
     <t>Bug ID</t>
   </si>
@@ -918,6 +918,165 @@
   </si>
   <si>
     <t>56abd35  58ecfef  3ba3a1c</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>titiling</t>
+  </si>
+  <si>
+    <t>fix titles</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-032.png</t>
+  </si>
+  <si>
+    <t>create account error</t>
+  </si>
+  <si>
+    <t>create account is going back to sign in and won't let person create the new account</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Blazor event and then attempts to establish the authentication cookie. If the cookie is not committed before navigation, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> sees an anonymous request and sends the new user back to sign-in.</t>
+    </r>
+  </si>
+  <si>
+    <t>591d24f</t>
+  </si>
+  <si>
+    <t>add timezone setting here for user to select the timezone region</t>
+  </si>
+  <si>
+    <t>need timezone area</t>
+  </si>
+  <si>
+    <t>on Save Profile the toaster pop message should last about 5 seconds or what a typical modern website does now, because this isn't useful as a signal after a while</t>
+  </si>
+  <si>
+    <t>save profile toaster pop</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-033.png</t>
+  </si>
+  <si>
+    <t>if Diabetic checked show this menu item, if unchecked hide it</t>
+  </si>
+  <si>
+    <t>diabetic program</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-034.png</t>
+  </si>
+  <si>
+    <t>if checked box open for edit leave default to 100, if unchecked hide this box</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-035.png</t>
+  </si>
+  <si>
+    <t>toggle buttons</t>
+  </si>
+  <si>
+    <t>toggle buttons should be to on or off for each value and reflected as such in all the other pages of the website that use or show these values, because a person maay not necessarily care for any or even all of these attributes</t>
+  </si>
+  <si>
+    <t>If Weight-loss focus is checked, hide the boxes marked with an X and reflect this on every page that uses or displays these values. Otherwise, show them and retain their default values.</t>
+  </si>
+  <si>
+    <t>weight loss</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-038.png</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-037.png</t>
+  </si>
+  <si>
+    <t>add sugar limit in database if checked show, if unchecked hide</t>
+  </si>
+  <si>
+    <t>sugar limit</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-039.png</t>
+  </si>
+  <si>
+    <t>c4ef2c7</t>
+  </si>
+  <si>
+    <t>remove default note because taking weight in afternoon doesn't reflect correctly</t>
+  </si>
+  <si>
+    <t>weight default note</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-040.png</t>
+  </si>
+  <si>
+    <t>since I realized that this webapp can handle more than just renal patients I don't want to save the JSON response maybe we show it but not save it</t>
+  </si>
+  <si>
+    <t>nutrition notes</t>
+  </si>
+  <si>
+    <t>docs/screenshots/AV-041.png</t>
+  </si>
+  <si>
+    <t>the estimate button is no longer working</t>
+  </si>
+  <si>
+    <t>estimate button</t>
+  </si>
+  <si>
+    <t>estimate button should appear disabled until person enters the item to look up</t>
+  </si>
+  <si>
+    <t>cdb28d2</t>
+  </si>
+  <si>
+    <t>HTTP 401
+invalid_api_key
+Replace OPENAI_API_KEY in the environment</t>
+  </si>
+  <si>
+    <t>9d1d259</t>
+  </si>
+  <si>
+    <t>b69a9b9</t>
+  </si>
+  <si>
+    <t>e5a4515</t>
+  </si>
+  <si>
+    <t>6827a9b</t>
+  </si>
+  <si>
+    <t>f4d1e28</t>
+  </si>
+  <si>
+    <t>3c6a9be</t>
+  </si>
+  <si>
+    <t>1e00673</t>
+  </si>
+  <si>
+    <t>aff118e</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1033,6 +1192,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1354,13 +1516,14 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="9" width="32" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="28.08203125" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="34" customWidth="1"/>
-    <col min="14" max="14" width="80.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="14" max="14" width="71.9140625" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
@@ -1470,10 +1633,10 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="4">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(B2="","",IF(Q2&lt;&gt;"",Q2-B2,TODAY()-B2))</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="28" hidden="1">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -1517,7 +1680,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="28" hidden="1">
@@ -1564,7 +1727,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="28" hidden="1">
@@ -1617,7 +1780,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="28" hidden="1">
@@ -1668,7 +1831,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="28" hidden="1">
@@ -1772,7 +1935,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="42" hidden="1">
@@ -1878,7 +2041,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="28" hidden="1">
@@ -2227,7 +2390,7 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="28" hidden="1">
@@ -2272,7 +2435,7 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="42" hidden="1">
@@ -2319,7 +2482,7 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="28" hidden="1">
@@ -2362,7 +2525,7 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="28" hidden="1">
@@ -2544,7 +2707,7 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="28" hidden="1">
@@ -2587,7 +2750,7 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:18" hidden="1">
@@ -2628,7 +2791,7 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="28" hidden="1">
@@ -2864,381 +3027,605 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" hidden="1">
       <c r="A32" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+      <c r="B32" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L32" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="P32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>46221</v>
+      </c>
+      <c r="R32" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="28" hidden="1">
       <c r="A33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
+      <c r="B33" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>277</v>
+      </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="N33" t="s">
+        <v>278</v>
+      </c>
+      <c r="O33" t="s">
+        <v>279</v>
+      </c>
       <c r="P33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>46221</v>
+      </c>
+      <c r="R33" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="28" hidden="1">
       <c r="A34" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
+      <c r="B34" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" s="2" t="s">
+        <v>309</v>
+      </c>
       <c r="P34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R34" s="4">
         <f t="shared" ref="R34:R51" ca="1" si="1">IF(B34="","",IF(Q34&lt;&gt;"",Q34-B34,TODAY()-B34))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="56" hidden="1">
       <c r="A35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
+      <c r="B35" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>282</v>
+      </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>284</v>
+      </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="P35" s="2" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="Q35" s="3"/>
-      <c r="R35" s="4" t="str">
+      <c r="R35" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="28" hidden="1">
       <c r="A36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
+      <c r="B36" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L36" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>287</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" s="2" t="s">
+        <v>313</v>
+      </c>
       <c r="P36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R36" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="28" hidden="1">
       <c r="A37" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="B37" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L37" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" s="2" t="s">
+        <v>314</v>
+      </c>
       <c r="P37" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R37" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="84" hidden="1">
       <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
+      <c r="B38" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L38" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>295</v>
+      </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" s="13" t="s">
+        <v>317</v>
+      </c>
       <c r="P38" s="2" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="Q38" s="3"/>
-      <c r="R38" s="4" t="str">
+      <c r="R38" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" hidden="1">
       <c r="A39" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
+      <c r="B39" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="G39" t="s">
+        <v>292</v>
+      </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L39" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>294</v>
+      </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" s="2" t="s">
+        <v>315</v>
+      </c>
       <c r="P39" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R39" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="28">
       <c r="A40" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
+      <c r="B40" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L40" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" s="2">
+        <v>3039394</v>
+      </c>
       <c r="P40" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R40" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="28" hidden="1">
       <c r="A41" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
+      <c r="B41" s="3">
+        <v>46222</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L41" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>302</v>
+      </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" s="2" t="s">
+        <v>316</v>
+      </c>
       <c r="P41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R41" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="56" hidden="1">
       <c r="A42" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
+      <c r="B42" s="3">
+        <v>46222</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="P42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R42" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="42" hidden="1">
       <c r="A43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
+      <c r="B43" s="3">
+        <v>46223</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>306</v>
+      </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
+      <c r="N43" s="2" t="s">
+        <v>310</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R43" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="28" hidden="1">
       <c r="A44" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
+      <c r="B44" s="3">
+        <v>46223</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>308</v>
+      </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" s="2" t="s">
+        <v>311</v>
+      </c>
       <c r="P44" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>46223</v>
+      </c>
+      <c r="R44" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -3565,7 +3952,7 @@
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('Bug Tracker'!F2:F51,"&lt;&gt;")</f>
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
@@ -3573,7 +3960,7 @@
       </c>
       <c r="E5" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D5)</f>
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
@@ -3581,7 +3968,7 @@
       </c>
       <c r="H5" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G5)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3606,7 +3993,7 @@
       </c>
       <c r="H6" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,G6)</f>
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3615,7 +4002,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"Critical")</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
@@ -3640,7 +4027,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Bug Tracker'!C2:C51,"High")</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5" t="s">
@@ -3705,7 +4092,7 @@
       </c>
       <c r="B11" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,"Closed")+COUNTIF('Bug Tracker'!K2:K51,"Verified")</f>
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5" t="s">
@@ -3743,7 +4130,7 @@
       </c>
       <c r="E13" s="5">
         <f>COUNTIF('Bug Tracker'!K2:K51,D13)</f>
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
